--- a/output/laminas_comunales/comunal_o_ocup_a_2021_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C358"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C2">
-        <v>54.5336165530844</v>
+        <v>69.93288486094239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C3">
-        <v>49.6259057430291</v>
+        <v>69.6364588501185</v>
       </c>
     </row>
     <row r="4">
@@ -414,727 +414,5317 @@
         </is>
       </c>
       <c r="C4">
-        <v>46.8396553388262</v>
+        <v>69.3060114971554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C5">
-        <v>46.6627424113565</v>
+        <v>68.78016437534561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C6">
-        <v>46.2858114937008</v>
+        <v>66.5960315586933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C7">
-        <v>46.2559993216315</v>
+        <v>64.6056537593936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C8">
-        <v>45.1870487858237</v>
+        <v>63.7886816807636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C9">
-        <v>43.8552095977494</v>
+        <v>62.6957655837422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C10">
-        <v>43.2018710840271</v>
+        <v>62.4231058339853</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C11">
-        <v>42.9717490815505</v>
+        <v>61.6891145185799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C12">
-        <v>42.786110502883</v>
+        <v>61.1070521518283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C13">
-        <v>42.6530205288238</v>
+        <v>61.0997919195422</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C14">
-        <v>42.0974344505329</v>
+        <v>60.6988676574664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C15">
-        <v>41.9504308548761</v>
+        <v>60.6806765761148</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C16">
-        <v>41.5141889396667</v>
+        <v>60.4775557657445</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C17">
-        <v>41.4436821843276</v>
+        <v>60.4076273923361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C18">
-        <v>41.2239510867885</v>
+        <v>60.3923089066984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="C19">
-        <v>41.0592908261711</v>
+        <v>60.2650842247168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C20">
-        <v>41.0561741609185</v>
+        <v>60.1259106676297</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C21">
-        <v>40.513164425758</v>
+        <v>59.9935583207642</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C22">
-        <v>40.3989326054905</v>
+        <v>59.8771131482336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C23">
-        <v>39.6866003783306</v>
+        <v>59.8166206987129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C24">
-        <v>39.6813105948481</v>
+        <v>59.7082542899959</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C25">
-        <v>39.6473541100188</v>
+        <v>59.1234951981604</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C26">
-        <v>39.4891614022049</v>
+        <v>58.6290519877676</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C27">
-        <v>39.1034788224718</v>
+        <v>58.567543841601</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C28">
-        <v>39.0647439769143</v>
+        <v>58.5456212746447</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C29">
-        <v>38.8027834888502</v>
+        <v>58.0812853891967</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C30">
-        <v>38.6947821585931</v>
+        <v>58.0279194398824</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C31">
-        <v>38.6774416647945</v>
+        <v>57.8862765617794</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C32">
-        <v>38.5779943375708</v>
+        <v>57.8243966101044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C33">
-        <v>37.7021689814437</v>
+        <v>57.4471204956193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C34">
-        <v>37.6574986741766</v>
+        <v>57.3243498582865</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="C35">
-        <v>37.6403853113951</v>
+        <v>56.6903460837887</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C36">
-        <v>37.5586048469836</v>
+        <v>56.1300603966628</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C37">
-        <v>36.974329333918</v>
+        <v>55.9771764801694</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C38">
-        <v>36.6423716558207</v>
+        <v>55.9302352858383</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C39">
-        <v>36.5690552106058</v>
+        <v>55.8265977420206</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="C40">
-        <v>36.5413618370805</v>
+        <v>55.5820699981284</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C41">
-        <v>36.1011292236995</v>
+        <v>55.5774021352313</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C42">
-        <v>34.9969639724734</v>
+        <v>55.2264394906544</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C43">
-        <v>34.9640312910295</v>
+        <v>54.9728229020159</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C44">
-        <v>34.6615492692792</v>
+        <v>54.8680413610677</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C45">
-        <v>34.6533018076936</v>
+        <v>54.5336165530844</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C46">
-        <v>34.4274598333293</v>
+        <v>54.2539493884019</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="C47">
-        <v>34.3594343604897</v>
+        <v>54.1976900741318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C48">
-        <v>33.7727558066541</v>
+        <v>54.1649862203401</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C49">
-        <v>33.6686119693329</v>
+        <v>54.1440095364065</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="C50">
-        <v>33.6347953216374</v>
+        <v>54.0174069143572</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C51">
-        <v>33.3495750094743</v>
+        <v>53.9238301478204</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>53.8061319939705</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>53.6924454498327</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>52.9616551802377</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>52.8809183696606</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>52.8220843610634</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>52.5959546300523</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>52.5375746345481</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>52.4800391228351</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>52.3323442136498</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>52.3135852911134</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>52.2789914250715</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>51.9045195823439</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>51.894527878474</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>51.6378197828892</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>51.5951024779709</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>51.490275893261</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>51.4163644087181</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>51.1183238665918</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>50.9258830475705</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>50.9102241064406</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>50.7684464516405</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>50.5870159482814</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>50.582368482937</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>50.4226698029991</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>50.3832640232772</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>50.3632238091888</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>50.2990076279345</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>50.2225506967166</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>49.9336303095752</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>49.8672416317911</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>49.8287406892825</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>49.8063232830821</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>49.6504095424959</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>49.6259057430291</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>49.4179848195145</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>48.8158033547843</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>48.7292268946314</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>48.7081476981234</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>48.600311440309</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>48.5207489455258</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>48.324322004806</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>48.3035624560346</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>48.1770080952624</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>48.1699961842866</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>48.0330282949406</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>47.9691142191142</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>47.9569575471698</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>47.9330460956139</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>47.9096496572442</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>47.8342434307775</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>47.7519487750557</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>47.6994565757176</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>47.6926752367736</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>47.1290215419211</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>47.0890681854137</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>47.0583653546578</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>46.9865931765696</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>46.9162119145066</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>46.9078655670834</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>46.8396553388262</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>46.781298136777</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>46.6959739221105</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>46.6627424113565</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>46.4220585181775</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>46.2858114937008</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>46.2559993216315</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>46.1781827385472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>46.1690974424012</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>45.8454258882681</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>45.8142292490119</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>45.8115873481858</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>45.7819663779929</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>45.6393291819983</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>45.5283875182015</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>45.3736692007259</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>45.1870487858237</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>45.1085716892478</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>44.7549710349147</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>44.7222420861937</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>44.5889738412824</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>44.471295532241</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>44.3720053628731</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>44.1450155443955</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>44.0361036169419</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>44.018059667896</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>43.8784458335207</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>43.8642535071711</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>43.8552095977494</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>43.5743044755486</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>43.5065664606132</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>43.4956500456133</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>43.4529603506197</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>43.4316906122869</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>43.4190229109331</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>43.2018710840271</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>43.1443562241724</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>13505</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="C52">
+      <c r="C148">
+        <v>43.1330290736984</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>42.9717490815505</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>42.7880114094106</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>42.786110502883</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>42.6824666690624</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>42.6530205288238</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>42.4938452779047</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>42.4640522875817</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>42.2502281021898</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>42.1665830793565</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>42.1552103180419</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>42.0974344505329</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>42.0926432512663</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>42.0553704585118</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>42.0380633491129</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>42.0220335365131</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>41.9884452245137</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>41.9504308548761</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>41.8964794635373</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>41.7008453790893</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>41.5469113024464</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>41.5141889396667</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>41.4436821843276</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>41.3837972391944</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>41.3008180030895</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>41.2239510867885</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>41.0592908261711</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>41.0561741609185</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>40.6875606512597</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>40.513164425758</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>40.4961748889044</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>40.3989326054905</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>40.3484908860552</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>40.336458882385</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>40.0297639318358</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>39.6866003783306</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>39.6813105948481</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>39.6473541100188</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>39.6467307776753</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>39.6215065704238</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>39.4891614022049</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>39.324617428608</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>39.1049968374447</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>39.1034788224718</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>39.0647439769143</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>38.8694434721736</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>38.8027834888502</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>38.728509789603</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>38.6947821585931</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>38.6774416647945</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>38.5779943375708</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>38.2392618705319</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>38.125624974712</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>38.1007330980179</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>37.9577307186617</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>37.7021689814437</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>37.6574986741766</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>37.6403853113951</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>37.5586048469836</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>37.5269030528202</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>37.4761989500845</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>37.4002234993614</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>37.1435049282833</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>37.059923598078</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>36.9910840287465</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>36.974329333918</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>36.8592762939155</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>36.8576008634098</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>36.8486969860152</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>36.6423716558207</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>36.6411304890465</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>36.5690552106058</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>36.5413618370805</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>36.2058926669181</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>36.2026886276171</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>36.1011292236995</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>36.0621811531427</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>36.0516168873225</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>35.9749678940609</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>35.9316195452708</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>35.8005097869475</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>35.6165920905918</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>35.4621691700343</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>35.1512500747652</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>34.9969639724734</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>34.9640312910295</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>34.8637928114301</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>34.81015031465</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>34.7393836102826</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>34.7132898497841</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>34.6996545547595</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>34.6926112694585</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>34.6615492692792</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>34.6566639632333</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>34.6533018076936</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>34.596221266601</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>34.5708503579983</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>34.4418855161263</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>34.4274598333293</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>34.4183954966542</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>34.3594343604897</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>34.2923716948678</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>34.0118436514317</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>33.9942911512845</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>33.9794353818918</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>33.9690352882627</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>33.8941053180923</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>33.8382688974405</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>33.7727558066541</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>33.6752519854268</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>33.6686119693329</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>33.6347953216374</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>33.3495750094743</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>32.7496961314389</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>32.6546745690434</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>32.636191614381</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>32.587720018165</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>32.5804995924071</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>32.4300833938434</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>32.4202031025797</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>32.398003852215</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>32.3700630387238</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>32.0281499779253</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>31.7886135472815</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>31.6880341880342</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>31.6823184893467</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>31.5132522753463</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>31.3606677783071</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>31.2972091742804</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>31.2672129152021</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>31.160452450775</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>31.0135713963659</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>31.0114942528736</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>31.0031659154325</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>30.726644770257</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>30.6671596417714</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>30.6359134740683</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>30.1157055271286</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>30.0003149894908</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>29.7998839907193</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>29.5286408793067</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>29.4111880799895</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>28.5563656375865</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>28.3770928462709</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>28.3743697971626</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>28.0089573865507</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>27.9596947574834</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>27.5972560700424</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>27.3425404906514</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>27.2732331663884</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>27.1332952670981</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>27.0564523508849</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>26.7238521465274</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>26.5860824148393</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>26.3889221867933</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>26.2776198175094</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>26.2459469877333</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C306">
         <v>25.8575476885336</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>20.7548814504881</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>19.8159427966102</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>17.6607264771985</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>16.3161101959366</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Calera de Tango</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>15.1451231859602</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>14.6112010605583</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>14.3695697145221</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>14.21496611535</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>13.9409745474748</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>13.8331763386006</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>13.762108429029</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>13.6089425124202</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>13123</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>13.5185068712853</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>13.2566388518931</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>13302</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>12.8457903780069</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>13402</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>12.6676185746213</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>13122</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>12.6307254823623</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>13130</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>12.5550019871686</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>12.4775915889726</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>12.3445837108628</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>13108</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>12.2616198970343</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>12.2127830842982</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>San José de Maipo</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>12.2086167800454</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>11.784375397128</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>11.7528641571195</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>13111</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>11.685346215781</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Isla de Maipo</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>11.5243271221532</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>11.494963187412</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Estación Central</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>11.4882220643939</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>11.4147083278631</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>11.3940572881798</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Quinta Normal</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>11.3407285675158</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>11.2454831565451</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>13102</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>11.2421936611463</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>11.1779653897849</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>13602</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>El Monte</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>11.172342150603</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>11.0697251315337</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>10.9049715382259</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>10.6984234442154</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Curacaví</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>10.4384816753927</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>10.4264562826664</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>10.4047912494223</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>13104</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>10.3085435391901</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>María Pinto</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>10.2154046997389</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>13105</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>10.0572198590119</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>10.0032698056801</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Alhué</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>9.96020599250936</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>9.95302425930107</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Lo Prado</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>9.885864865305861</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>9.522330211985381</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>8.991847826086961</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>6.25958295001533</v>
       </c>
     </row>
   </sheetData>
